--- a/三鷹駅南口_平日_時刻表.xlsx
+++ b/三鷹駅南口_平日_時刻表.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -206,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,6 +254,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1390,15 +1403,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>28
+鷹52</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>38
+鷹63</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>48
+鷹51</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>56
+鷹51</t>
+        </is>
+      </c>
       <c r="G12" s="20" t="n"/>
       <c r="H12" s="20" t="n"/>
       <c r="I12" s="20" t="n"/>
@@ -1409,17 +1446,50 @@
       <c r="N12" s="20" t="n"/>
       <c r="O12" s="20" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>08
+鷹63</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>13
+鷹55</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>32
+鷹51</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>38
+鷹51</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹60</t>
+        </is>
+      </c>
       <c r="I13" s="20" t="n"/>
       <c r="J13" s="20" t="n"/>
       <c r="K13" s="20" t="n"/>
@@ -1428,16 +1498,46 @@
       <c r="N13" s="20" t="n"/>
       <c r="O13" s="20" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>03
+鷹51</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>10
+鷹60</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹65</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>34
+鷹55</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹54</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>55
+鷹51</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="n"/>
       <c r="I14" s="20" t="n"/>
       <c r="J14" s="20" t="n"/>
@@ -1447,15 +1547,40 @@
       <c r="N14" s="20" t="n"/>
       <c r="O14" s="20" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>00
+鷹63</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹59</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>30
+鷹59</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹63</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹63</t>
+        </is>
+      </c>
       <c r="G15" s="20" t="n"/>
       <c r="H15" s="20" t="n"/>
       <c r="I15" s="20" t="n"/>
@@ -1466,14 +1591,33 @@
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹51</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>30
+鷹57</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹51</t>
+        </is>
+      </c>
       <c r="F16" s="20" t="n"/>
       <c r="G16" s="20" t="n"/>
       <c r="H16" s="20" t="n"/>
@@ -1485,16 +1629,44 @@
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>08
+鷹54</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>23
+鷹53</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹63</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>55
+鷹61</t>
+        </is>
+      </c>
       <c r="H17" s="20" t="n"/>
       <c r="I17" s="20" t="n"/>
       <c r="J17" s="20" t="n"/>
@@ -1504,18 +1676,54 @@
       <c r="N17" s="20" t="n"/>
       <c r="O17" s="20" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="20" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>08
+鷹51</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>20
+鷹51</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>35
+鷹55</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹61</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="J18" s="20" t="n"/>
       <c r="K18" s="20" t="n"/>
       <c r="L18" s="20" t="n"/>
@@ -1523,17 +1731,49 @@
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>12
+鷹65</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹63</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹52</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>57
+鷹61</t>
+        </is>
+      </c>
       <c r="I19" s="20" t="n"/>
       <c r="J19" s="20" t="n"/>
       <c r="K19" s="20" t="n"/>
@@ -1542,17 +1782,49 @@
       <c r="N19" s="20" t="n"/>
       <c r="O19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="20" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>09
+鷹55</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>20
+鷹52</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>27
+鷹62</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>42
+鷹62</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="I20" s="20" t="n"/>
       <c r="J20" s="20" t="n"/>
       <c r="K20" s="20" t="n"/>
@@ -1561,16 +1833,43 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>12
+鷹54</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>35
+鷹54</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹63</t>
+        </is>
+      </c>
       <c r="H21" s="20" t="n"/>
       <c r="I21" s="20" t="n"/>
       <c r="J21" s="20" t="n"/>
@@ -1580,16 +1879,42 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>12
+鷹51</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>55
+鷹62</t>
+        </is>
+      </c>
       <c r="H22" s="20" t="n"/>
       <c r="I22" s="20" t="n"/>
       <c r="J22" s="20" t="n"/>
@@ -1599,16 +1924,43 @@
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="20" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>14
+鷹61</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>40
+鷹54</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>57
+鷹57</t>
+        </is>
+      </c>
       <c r="H23" s="20" t="n"/>
       <c r="I23" s="20" t="n"/>
       <c r="J23" s="20" t="n"/>
@@ -1618,16 +1970,43 @@
       <c r="N23" s="20" t="n"/>
       <c r="O23" s="20" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>11
+鷹54</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹62</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>55
+鷹63</t>
+        </is>
+      </c>
       <c r="H24" s="20" t="n"/>
       <c r="I24" s="20" t="n"/>
       <c r="J24" s="20" t="n"/>
@@ -1637,16 +2016,43 @@
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="20" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>05
+鷹63</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>23
+鷹51</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>55
+鷹63</t>
+        </is>
+      </c>
       <c r="H25" s="20" t="n"/>
       <c r="I25" s="20" t="n"/>
       <c r="J25" s="20" t="n"/>
@@ -1656,14 +2062,32 @@
       <c r="N25" s="20" t="n"/>
       <c r="O25" s="20" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>09
+鷹51</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹54</t>
+        </is>
+      </c>
       <c r="F26" s="20" t="n"/>
       <c r="G26" s="20" t="n"/>
       <c r="H26" s="20" t="n"/>
@@ -1675,14 +2099,32 @@
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="20" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>14
+鷹54</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>31
+鷹55</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="F27" s="20" t="n"/>
       <c r="G27" s="20" t="n"/>
       <c r="H27" s="20" t="n"/>
@@ -1694,12 +2136,21 @@
       <c r="N27" s="20" t="n"/>
       <c r="O27" s="20" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>10
+鷹54</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="20" t="n"/>
       <c r="F28" s="20" t="n"/>
@@ -1713,11 +2164,15 @@
       <c r="N28" s="20" t="n"/>
       <c r="O28" s="20" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="20" t="n"/>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="20" t="n"/>
       <c r="E29" s="20" t="n"/>
@@ -1732,11 +2187,16 @@
       <c r="N29" s="20" t="n"/>
       <c r="O29" s="20" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="20" t="n"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>鷹54
+植</t>
+        </is>
+      </c>
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="20" t="n"/>
       <c r="E30" s="20" t="n"/>

--- a/三鷹駅南口_平日_時刻表.xlsx
+++ b/三鷹駅南口_平日_時刻表.xlsx
@@ -3022,13 +3022,27 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>25
+鷹54</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>55
+鷹62</t>
+        </is>
+      </c>
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="20" t="n"/>
       <c r="G14" s="20" t="n"/>
@@ -3041,16 +3055,44 @@
       <c r="N14" s="20" t="n"/>
       <c r="O14" s="20" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>10
+鷹51</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>20
+鷹57</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>40
+鷹62</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>54
+鷹56</t>
+        </is>
+      </c>
       <c r="H15" s="20" t="n"/>
       <c r="I15" s="20" t="n"/>
       <c r="J15" s="20" t="n"/>
@@ -3060,34 +3102,98 @@
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>12
+鷹61</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>18
+鷹56</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>24
+鷹60</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹61</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹59</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="K16" s="20" t="n"/>
       <c r="L16" s="20" t="n"/>
       <c r="M16" s="20" t="n"/>
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹61</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>20
+鷹65</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>40
+鷹54</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="G17" s="20" t="n"/>
       <c r="H17" s="20" t="n"/>
       <c r="I17" s="20" t="n"/>
@@ -3098,15 +3204,36 @@
       <c r="N17" s="20" t="n"/>
       <c r="O17" s="20" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>14
+鷹65</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="G18" s="20" t="n"/>
       <c r="H18" s="20" t="n"/>
       <c r="I18" s="20" t="n"/>
@@ -3117,15 +3244,37 @@
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹55</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹54</t>
+        </is>
+      </c>
       <c r="G19" s="20" t="n"/>
       <c r="H19" s="20" t="n"/>
       <c r="I19" s="20" t="n"/>
@@ -3136,15 +3285,37 @@
       <c r="N19" s="20" t="n"/>
       <c r="O19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹65</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>26
+鷹61</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="G20" s="20" t="n"/>
       <c r="H20" s="20" t="n"/>
       <c r="I20" s="20" t="n"/>
@@ -3155,16 +3326,43 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>26
+鷹63</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>40
+鷹52</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H21" s="20" t="n"/>
       <c r="I21" s="20" t="n"/>
       <c r="J21" s="20" t="n"/>
@@ -3174,16 +3372,42 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>20
+鷹57</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H22" s="20" t="n"/>
       <c r="I22" s="20" t="n"/>
       <c r="J22" s="20" t="n"/>
@@ -3193,16 +3417,41 @@
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="20" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H23" s="20" t="n"/>
       <c r="I23" s="20" t="n"/>
       <c r="J23" s="20" t="n"/>
@@ -3212,16 +3461,41 @@
       <c r="N23" s="20" t="n"/>
       <c r="O23" s="20" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="H24" s="20" t="n"/>
       <c r="I24" s="20" t="n"/>
       <c r="J24" s="20" t="n"/>
@@ -3231,17 +3505,47 @@
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="20" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹54</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>58
+鷹61</t>
+        </is>
+      </c>
       <c r="I25" s="20" t="n"/>
       <c r="J25" s="20" t="n"/>
       <c r="K25" s="20" t="n"/>
@@ -3250,17 +3554,47 @@
       <c r="N25" s="20" t="n"/>
       <c r="O25" s="20" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="20" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>06
+鷹53</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>54
+鷹55</t>
+        </is>
+      </c>
       <c r="I26" s="20" t="n"/>
       <c r="J26" s="20" t="n"/>
       <c r="K26" s="20" t="n"/>
@@ -3269,15 +3603,37 @@
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="20" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹52</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>26
+鷹52</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="G27" s="20" t="n"/>
       <c r="H27" s="20" t="n"/>
       <c r="I27" s="20" t="n"/>
@@ -3288,14 +3644,32 @@
       <c r="N27" s="20" t="n"/>
       <c r="O27" s="20" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>06
+鷹52</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>16
+鷹52</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="F28" s="20" t="n"/>
       <c r="G28" s="20" t="n"/>
       <c r="H28" s="20" t="n"/>
@@ -3307,13 +3681,27 @@
       <c r="N28" s="20" t="n"/>
       <c r="O28" s="20" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>06
+鷹52</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>36
+鷹61</t>
+        </is>
+      </c>
       <c r="E29" s="20" t="n"/>
       <c r="F29" s="20" t="n"/>
       <c r="G29" s="20" t="n"/>
@@ -3326,13 +3714,27 @@
       <c r="N29" s="20" t="n"/>
       <c r="O29" s="20" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>09
+鷹54</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>26
+鷹52</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="E30" s="20" t="n"/>
       <c r="F30" s="20" t="n"/>
       <c r="G30" s="20" t="n"/>
@@ -3345,13 +3747,26 @@
       <c r="N30" s="20" t="n"/>
       <c r="O30" s="20" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>26
+鷹52</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="E31" s="20" t="n"/>
       <c r="F31" s="20" t="n"/>
       <c r="G31" s="20" t="n"/>
@@ -3617,12 +4032,22 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>40
+鷹53</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>55
+鷹51</t>
+        </is>
+      </c>
       <c r="D14" s="20" t="n"/>
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="20" t="n"/>
@@ -3636,18 +4061,56 @@
       <c r="N14" s="20" t="n"/>
       <c r="O14" s="20" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>09
+鷹59</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>18
+鷹51</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>23
+鷹55</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>40
+鷹56</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹54</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>51
+鷹65</t>
+        </is>
+      </c>
       <c r="J15" s="20" t="n"/>
       <c r="K15" s="20" t="n"/>
       <c r="L15" s="20" t="n"/>
@@ -3655,17 +4118,52 @@
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>04
+鷹60</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>08
+鷹56</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>20
+鷹55</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>24
+鷹51</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>37
+鷹56</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>46
+鷹51</t>
+        </is>
+      </c>
       <c r="I16" s="20" t="n"/>
       <c r="J16" s="20" t="n"/>
       <c r="K16" s="20" t="n"/>
@@ -3674,13 +4172,28 @@
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>06
+鷹56</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>26
+鷹53</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>46
+鷹56</t>
+        </is>
+      </c>
       <c r="E17" s="20" t="n"/>
       <c r="F17" s="20" t="n"/>
       <c r="G17" s="20" t="n"/>
@@ -3693,13 +4206,26 @@
       <c r="N17" s="20" t="n"/>
       <c r="O17" s="20" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>06
+鷹56</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="20" t="n"/>
       <c r="G18" s="20" t="n"/>
@@ -3712,13 +4238,28 @@
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>14
+鷹63</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>34
+鷹51</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>46
+鷹62</t>
+        </is>
+      </c>
       <c r="E19" s="20" t="n"/>
       <c r="F19" s="20" t="n"/>
       <c r="G19" s="20" t="n"/>
@@ -3731,13 +4272,26 @@
       <c r="N19" s="20" t="n"/>
       <c r="O19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>54
+鷹57</t>
+        </is>
+      </c>
       <c r="E20" s="20" t="n"/>
       <c r="F20" s="20" t="n"/>
       <c r="G20" s="20" t="n"/>
@@ -3750,13 +4304,27 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>09
+鷹57</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>47
+鷹54</t>
+        </is>
+      </c>
       <c r="E21" s="20" t="n"/>
       <c r="F21" s="20" t="n"/>
       <c r="G21" s="20" t="n"/>
@@ -3769,13 +4337,26 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>06
+鷹63</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="20" t="n"/>
       <c r="G22" s="20" t="n"/>
@@ -3788,13 +4369,25 @@
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="20" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="E23" s="20" t="n"/>
       <c r="F23" s="20" t="n"/>
       <c r="G23" s="20" t="n"/>
@@ -3807,14 +4400,32 @@
       <c r="N23" s="20" t="n"/>
       <c r="O23" s="20" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>05
+鷹53</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹63</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="F24" s="20" t="n"/>
       <c r="G24" s="20" t="n"/>
       <c r="H24" s="20" t="n"/>
@@ -3826,17 +4437,48 @@
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="20" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>12
+鷹51</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>42
+鷹56</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>57
+鷹62</t>
+        </is>
+      </c>
       <c r="I25" s="20" t="n"/>
       <c r="J25" s="20" t="n"/>
       <c r="K25" s="20" t="n"/>
@@ -3845,14 +4487,34 @@
       <c r="N25" s="20" t="n"/>
       <c r="O25" s="20" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>04
+鷹57</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>16
+鷹51</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>41
+鷹53</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>50
+鷹65</t>
+        </is>
+      </c>
       <c r="F26" s="20" t="n"/>
       <c r="G26" s="20" t="n"/>
       <c r="H26" s="20" t="n"/>
@@ -3864,13 +4526,27 @@
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="20" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>04
+鷹54</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>40
+鷹56</t>
+        </is>
+      </c>
       <c r="E27" s="20" t="n"/>
       <c r="F27" s="20" t="n"/>
       <c r="G27" s="20" t="n"/>
@@ -3883,12 +4559,21 @@
       <c r="N27" s="20" t="n"/>
       <c r="O27" s="20" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>04
+鷹56</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="20" t="n"/>
       <c r="F28" s="20" t="n"/>
@@ -3902,13 +4587,27 @@
       <c r="N28" s="20" t="n"/>
       <c r="O28" s="20" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>06
+鷹63</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹54</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="E29" s="20" t="n"/>
       <c r="F29" s="20" t="n"/>
       <c r="G29" s="20" t="n"/>
@@ -3921,14 +4620,32 @@
       <c r="N29" s="20" t="n"/>
       <c r="O29" s="20" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>06
+鷹56</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹60</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="F30" s="20" t="n"/>
       <c r="G30" s="20" t="n"/>
       <c r="H30" s="20" t="n"/>
@@ -4227,14 +4944,33 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>22
+鷹51</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>34
+鷹63</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>54
+鷹51</t>
+        </is>
+      </c>
       <c r="F15" s="20" t="n"/>
       <c r="G15" s="20" t="n"/>
       <c r="H15" s="20" t="n"/>
@@ -4246,18 +4982,55 @@
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>24
+鷹53</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>32
+鷹63</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>37
+鷹56</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>44
+鷹57</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>52
+鷹52</t>
+        </is>
+      </c>
       <c r="J16" s="20" t="n"/>
       <c r="K16" s="20" t="n"/>
       <c r="L16" s="20" t="n"/>
@@ -4265,16 +5038,44 @@
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>34
+鷹51</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>39
+鷹55</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>46
+鷹54</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>52
+鷹52</t>
+        </is>
+      </c>
       <c r="H17" s="20" t="n"/>
       <c r="I17" s="20" t="n"/>
       <c r="J17" s="20" t="n"/>
@@ -4284,15 +5085,37 @@
       <c r="N17" s="20" t="n"/>
       <c r="O17" s="20" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹63</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>52
+鷹57</t>
+        </is>
+      </c>
       <c r="G18" s="20" t="n"/>
       <c r="H18" s="20" t="n"/>
       <c r="I18" s="20" t="n"/>
@@ -4303,16 +5126,43 @@
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>05
+鷹56</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>12
+鷹63</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹62</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="H19" s="20" t="n"/>
       <c r="I19" s="20" t="n"/>
       <c r="J19" s="20" t="n"/>
@@ -4322,15 +5172,36 @@
       <c r="N19" s="20" t="n"/>
       <c r="O19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹63</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="G20" s="20" t="n"/>
       <c r="H20" s="20" t="n"/>
       <c r="I20" s="20" t="n"/>
@@ -4341,15 +5212,37 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>05
+鷹56</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>13
+鷹51</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="G21" s="20" t="n"/>
       <c r="H21" s="20" t="n"/>
       <c r="I21" s="20" t="n"/>
@@ -4360,15 +5253,36 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>16
+鷹51</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="G22" s="20" t="n"/>
       <c r="H22" s="20" t="n"/>
       <c r="I22" s="20" t="n"/>
@@ -4379,15 +5293,37 @@
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="20" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>18
+鷹54</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>40
+鷹53</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="G23" s="20" t="n"/>
       <c r="H23" s="20" t="n"/>
       <c r="I23" s="20" t="n"/>
@@ -4398,15 +5334,36 @@
       <c r="N23" s="20" t="n"/>
       <c r="O23" s="20" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>52
+鷹55</t>
+        </is>
+      </c>
       <c r="G24" s="20" t="n"/>
       <c r="H24" s="20" t="n"/>
       <c r="I24" s="20" t="n"/>
@@ -4417,15 +5374,36 @@
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="20" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>10
+鷹65</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="G25" s="20" t="n"/>
       <c r="H25" s="20" t="n"/>
       <c r="I25" s="20" t="n"/>
@@ -4436,15 +5414,36 @@
       <c r="N25" s="20" t="n"/>
       <c r="O25" s="20" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹63</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="G26" s="20" t="n"/>
       <c r="H26" s="20" t="n"/>
       <c r="I26" s="20" t="n"/>
@@ -4455,15 +5454,37 @@
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="20" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>16
+鷹56</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹52</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="G27" s="20" t="n"/>
       <c r="H27" s="20" t="n"/>
       <c r="I27" s="20" t="n"/>
@@ -4474,14 +5495,31 @@
       <c r="N27" s="20" t="n"/>
       <c r="O27" s="20" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>08
+鷹57</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="F28" s="20" t="n"/>
       <c r="G28" s="20" t="n"/>
       <c r="H28" s="20" t="n"/>
@@ -4493,13 +5531,26 @@
       <c r="N28" s="20" t="n"/>
       <c r="O28" s="20" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹65</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="E29" s="20" t="n"/>
       <c r="F29" s="20" t="n"/>
       <c r="G29" s="20" t="n"/>
@@ -4512,13 +5563,26 @@
       <c r="N29" s="20" t="n"/>
       <c r="O29" s="20" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹53</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="E30" s="20" t="n"/>
       <c r="F30" s="20" t="n"/>
       <c r="G30" s="20" t="n"/>
@@ -4531,11 +5595,16 @@
       <c r="N30" s="20" t="n"/>
       <c r="O30" s="20" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="20" t="n"/>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>21
+鷹51</t>
+        </is>
+      </c>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="20" t="n"/>
       <c r="E31" s="20" t="n"/>
@@ -4550,11 +5619,15 @@
       <c r="N31" s="20" t="n"/>
       <c r="O31" s="20" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="20" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="20" t="n"/>
       <c r="E32" s="20" t="n"/>
@@ -4793,13 +5866,26 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹53</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E12" s="20" t="n"/>
       <c r="F12" s="20" t="n"/>
       <c r="G12" s="20" t="n"/>
@@ -4812,15 +5898,38 @@
       <c r="N12" s="20" t="n"/>
       <c r="O12" s="20" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹52</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹63</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>35
+鷹56</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="G13" s="20" t="n"/>
       <c r="H13" s="20" t="n"/>
       <c r="I13" s="20" t="n"/>
@@ -4831,14 +5940,32 @@
       <c r="N13" s="20" t="n"/>
       <c r="O13" s="20" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>01
+鷹59</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>31
+鷹56</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="F14" s="20" t="n"/>
       <c r="G14" s="20" t="n"/>
       <c r="H14" s="20" t="n"/>
@@ -4850,13 +5977,28 @@
       <c r="N14" s="20" t="n"/>
       <c r="O14" s="20" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>31
+鷹54</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>41
+鷹60</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹56</t>
+        </is>
+      </c>
       <c r="E15" s="20" t="n"/>
       <c r="F15" s="20" t="n"/>
       <c r="G15" s="20" t="n"/>
@@ -4869,16 +6011,43 @@
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>24
+鷹54</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>30
+鷹51</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="n"/>
       <c r="I16" s="20" t="n"/>
       <c r="J16" s="20" t="n"/>
@@ -4888,15 +6057,36 @@
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹57</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="G17" s="20" t="n"/>
       <c r="H17" s="20" t="n"/>
       <c r="I17" s="20" t="n"/>
@@ -4907,14 +6097,32 @@
       <c r="N17" s="20" t="n"/>
       <c r="O17" s="20" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹51</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>42
+鷹56</t>
+        </is>
+      </c>
       <c r="F18" s="20" t="n"/>
       <c r="G18" s="20" t="n"/>
       <c r="H18" s="20" t="n"/>
@@ -4926,14 +6134,31 @@
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>13
+鷹52</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="F19" s="20" t="n"/>
       <c r="G19" s="20" t="n"/>
       <c r="H19" s="20" t="n"/>
@@ -4945,16 +6170,41 @@
       <c r="N19" s="20" t="n"/>
       <c r="O19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>11
+鷹61</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="H20" s="20" t="n"/>
       <c r="I20" s="20" t="n"/>
       <c r="J20" s="20" t="n"/>
@@ -4964,14 +6214,33 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹51</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>11
+鷹63</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹52</t>
+        </is>
+      </c>
       <c r="F21" s="20" t="n"/>
       <c r="G21" s="20" t="n"/>
       <c r="H21" s="20" t="n"/>
@@ -4983,14 +6252,33 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹57</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>23
+鷹65</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹52</t>
+        </is>
+      </c>
       <c r="F22" s="20" t="n"/>
       <c r="G22" s="20" t="n"/>
       <c r="H22" s="20" t="n"/>
@@ -5002,14 +6290,32 @@
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="20" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>14
+鷹54</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>20
+鷹52</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F23" s="20" t="n"/>
       <c r="G23" s="20" t="n"/>
       <c r="H23" s="20" t="n"/>
@@ -5021,15 +6327,37 @@
       <c r="N23" s="20" t="n"/>
       <c r="O23" s="20" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>16
+鷹62</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="G24" s="20" t="n"/>
       <c r="H24" s="20" t="n"/>
       <c r="I24" s="20" t="n"/>
@@ -5040,14 +6368,32 @@
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="20" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>00
+鷹56</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>22
+鷹62</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F25" s="20" t="n"/>
       <c r="G25" s="20" t="n"/>
       <c r="H25" s="20" t="n"/>
@@ -5059,13 +6405,26 @@
       <c r="N25" s="20" t="n"/>
       <c r="O25" s="20" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>05
+鷹56</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="E26" s="20" t="n"/>
       <c r="F26" s="20" t="n"/>
       <c r="G26" s="20" t="n"/>
@@ -5078,14 +6437,32 @@
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="20" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>06
+鷹52</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>24
+鷹54</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F27" s="20" t="n"/>
       <c r="G27" s="20" t="n"/>
       <c r="H27" s="20" t="n"/>
@@ -5097,11 +6474,16 @@
       <c r="N27" s="20" t="n"/>
       <c r="O27" s="20" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="20" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>10
+鷹52</t>
+        </is>
+      </c>
       <c r="C28" s="20" t="n"/>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="20" t="n"/>

--- a/三鷹駅南口_平日_時刻表.xlsx
+++ b/三鷹駅南口_平日_時刻表.xlsx
@@ -1461,15 +1461,16 @@
 鷹63</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>13
 鷹55</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>22</t>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>22
+鷹65</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -1484,7 +1485,7 @@
 鷹51</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>50
 鷹60</t>
@@ -1514,7 +1515,7 @@
 鷹60</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>15
 鷹65</t>
@@ -1535,7 +1536,7 @@
       <c r="G14" s="23" t="inlineStr">
         <is>
           <t>55
-鷹51</t>
+鷹62</t>
         </is>
       </c>
       <c r="H14" s="20" t="n"/>
@@ -1563,19 +1564,19 @@
 鷹59</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>30
 鷹59</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>45
 鷹63</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>50
 鷹63</t>
@@ -1633,7 +1634,7 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>00</t>
         </is>
@@ -1644,10 +1645,10 @@
 鷹54</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>23
-鷹53</t>
+鷹51</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -1658,16 +1659,21 @@
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t>45
+鷹52</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>52
 鷹63</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>55
-鷹61</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="n"/>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>59
+鷹63</t>
+        </is>
+      </c>
       <c r="I17" s="20" t="n"/>
       <c r="J17" s="20" t="n"/>
       <c r="K17" s="20" t="n"/>
@@ -1680,46 +1686,46 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>08
 鷹51</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>20
 鷹51</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>35
 鷹55</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>50
 鷹61</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>57</t>
         </is>
@@ -1737,10 +1743,11 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
+          <t>00
+鷹55</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>12
 鷹65</t>
@@ -1751,7 +1758,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>30
 鷹63</t>
@@ -1762,7 +1769,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>50
 鷹52</t>
@@ -1771,7 +1778,7 @@
       <c r="H19" s="23" t="inlineStr">
         <is>
           <t>57
-鷹61</t>
+鷹62</t>
         </is>
       </c>
       <c r="I19" s="20" t="n"/>
@@ -1786,35 +1793,35 @@
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>09
 鷹55</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>20
 鷹52</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>27
 鷹62</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>42
 鷹62</t>
@@ -1839,38 +1846,42 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05
+鷹51</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>12
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>20
 鷹54</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>35
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>42
 鷹54</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>50
-鷹63</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="n"/>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="I21" s="20" t="n"/>
       <c r="J21" s="20" t="n"/>
       <c r="K21" s="20" t="n"/>
@@ -1896,26 +1907,31 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22
+鷹56</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>55
 鷹62</t>
         </is>
       </c>
-      <c r="H22" s="20" t="n"/>
       <c r="I22" s="20" t="n"/>
       <c r="J22" s="20" t="n"/>
       <c r="K22" s="20" t="n"/>
@@ -1930,13 +1946,13 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00
+鷹56</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>14
-鷹61</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -1946,8 +1962,7 @@
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>40
-鷹54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -1957,11 +1972,15 @@
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
           <t>57
-鷹57</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="n"/>
+鷹62</t>
+        </is>
+      </c>
       <c r="I23" s="20" t="n"/>
       <c r="J23" s="20" t="n"/>
       <c r="K23" s="20" t="n"/>
@@ -1981,30 +2000,30 @@
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>11
-鷹54</t>
+          <t>06
+鷹53</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>48
-鷹62</t>
+          <t>36
+鷹52</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>55
-鷹63</t>
+          <t>50
+鷹52</t>
         </is>
       </c>
       <c r="H24" s="20" t="n"/>
@@ -2022,38 +2041,43 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>05
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>11
 鷹63</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
           <t>23
-鷹51</t>
+鷹55</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹62</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>55
 鷹63</t>
         </is>
       </c>
-      <c r="H25" s="20" t="n"/>
       <c r="I25" s="20" t="n"/>
       <c r="J25" s="20" t="n"/>
       <c r="K25" s="20" t="n"/>
@@ -2068,7 +2092,7 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -2079,16 +2103,20 @@
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>48
 鷹54</t>
         </is>
       </c>
-      <c r="F26" s="20" t="n"/>
       <c r="G26" s="20" t="n"/>
       <c r="H26" s="20" t="n"/>
       <c r="I26" s="20" t="n"/>
@@ -2105,28 +2133,37 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
           <t>14
 鷹54</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>31
-鷹55</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
+鷹56</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>53
+鷹54</t>
+        </is>
+      </c>
       <c r="H27" s="20" t="n"/>
       <c r="I27" s="20" t="n"/>
       <c r="J27" s="20" t="n"/>
@@ -2143,15 +2180,19 @@
       <c r="B28" s="23" t="inlineStr">
         <is>
           <t>10
-鷹54</t>
+鷹55</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="E28" s="20" t="n"/>
       <c r="F28" s="20" t="n"/>
       <c r="G28" s="20" t="n"/>
@@ -2168,11 +2209,7 @@
       <c r="A29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="B29" s="21" t="n"/>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="20" t="n"/>
       <c r="E29" s="20" t="n"/>
@@ -2193,8 +2230,8 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>鷹54
-植</t>
+          <t>09
+鷹54植</t>
         </is>
       </c>
       <c r="C30" s="20" t="n"/>

--- a/三鷹駅南口_平日_時刻表.xlsx
+++ b/三鷹駅南口_平日_時刻表.xlsx
@@ -2465,12 +2465,21 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>52
+鷹56</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="D13" s="20" t="n"/>
       <c r="E13" s="20" t="n"/>
       <c r="F13" s="20" t="n"/>
@@ -2484,17 +2493,50 @@
       <c r="N13" s="20" t="n"/>
       <c r="O13" s="20" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>08
+鷹54</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>21
+鷹51</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>25
+鷹59</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹63</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>48
+鷹59</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="I14" s="20" t="n"/>
       <c r="J14" s="20" t="n"/>
       <c r="K14" s="20" t="n"/>
@@ -2503,17 +2545,49 @@
       <c r="N14" s="20" t="n"/>
       <c r="O14" s="20" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹51</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>19
+鷹52</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹54</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>53
+鷹55</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="I15" s="20" t="n"/>
       <c r="J15" s="20" t="n"/>
       <c r="K15" s="20" t="n"/>
@@ -2522,15 +2596,38 @@
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹54</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹54</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>53
+鷹53</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="G16" s="20" t="n"/>
       <c r="H16" s="20" t="n"/>
       <c r="I16" s="20" t="n"/>
@@ -2541,14 +2638,32 @@
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>28
+鷹53</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹54</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="F17" s="20" t="n"/>
       <c r="G17" s="20" t="n"/>
       <c r="H17" s="20" t="n"/>
@@ -2560,16 +2675,43 @@
       <c r="N17" s="20" t="n"/>
       <c r="O17" s="20" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹56</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>37
+鷹54</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹51</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="H18" s="20" t="n"/>
       <c r="I18" s="20" t="n"/>
       <c r="J18" s="20" t="n"/>
@@ -2579,15 +2721,36 @@
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹54</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="G19" s="20" t="n"/>
       <c r="H19" s="20" t="n"/>
       <c r="I19" s="20" t="n"/>
@@ -2598,15 +2761,38 @@
       <c r="N19" s="20" t="n"/>
       <c r="O19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>15
+鷹63</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹63</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>53
+鷹53</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="G20" s="20" t="n"/>
       <c r="H20" s="20" t="n"/>
       <c r="I20" s="20" t="n"/>
@@ -2617,15 +2803,38 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>04
+鷹53</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>27
+鷹63</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>45
+鷹63</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="G21" s="20" t="n"/>
       <c r="H21" s="20" t="n"/>
       <c r="I21" s="20" t="n"/>
@@ -2636,14 +2845,33 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹61</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>18
+鷹51</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹61</t>
+        </is>
+      </c>
       <c r="F22" s="20" t="n"/>
       <c r="G22" s="20" t="n"/>
       <c r="H22" s="20" t="n"/>
@@ -2655,16 +2883,43 @@
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="20" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>02
+鷹51</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹52</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>58
+鷹63</t>
+        </is>
+      </c>
       <c r="H23" s="20" t="n"/>
       <c r="I23" s="20" t="n"/>
       <c r="J23" s="20" t="n"/>
@@ -2674,15 +2929,38 @@
       <c r="N23" s="20" t="n"/>
       <c r="O23" s="20" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹56</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹62</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>48
+鷹59</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="G24" s="20" t="n"/>
       <c r="H24" s="20" t="n"/>
       <c r="I24" s="20" t="n"/>
@@ -2693,14 +2971,33 @@
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="20" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>11
+鷹60</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>42
+鷹56</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>45
+鷹54</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="F25" s="20" t="n"/>
       <c r="G25" s="20" t="n"/>
       <c r="H25" s="20" t="n"/>
@@ -2712,14 +3009,32 @@
       <c r="N25" s="20" t="n"/>
       <c r="O25" s="20" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>04
+鷹53</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>35
+鷹61</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F26" s="20" t="n"/>
       <c r="G26" s="20" t="n"/>
       <c r="H26" s="20" t="n"/>
@@ -2731,15 +3046,37 @@
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="20" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>15
+鷹63</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>32
+鷹51</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="G27" s="20" t="n"/>
       <c r="H27" s="20" t="n"/>
       <c r="I27" s="20" t="n"/>
@@ -2750,14 +3087,32 @@
       <c r="N27" s="20" t="n"/>
       <c r="O27" s="20" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>17
+鷹62</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>31
+鷹51</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="F28" s="20" t="n"/>
       <c r="G28" s="20" t="n"/>
       <c r="H28" s="20" t="n"/>
